--- a/samples/excel/試用資料_正確.xlsx
+++ b/samples/excel/試用資料_正確.xlsx
@@ -2,27 +2,27 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="說明" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="承保資料" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="給付資料" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="保單資料" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="理賠資料" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="客戶資料" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="商品資料" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="上年度承保資料" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="控制總數" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="去年保單資料" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="系統總數" sheetId="7" state="visible" r:id="rId9"/>
     <sheet name="資產負債表" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">上年度承保資料!$A$1:$BI$108</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">保單資料!$A$1:$BI$154</definedName>
+    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">去年保單資料!$A$1:$BI$108</definedName>
     <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">商品資料!$A$1:$G$15</definedName>
     <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">客戶資料!$A$1:$I$241</definedName>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">承保資料!$A$1:$BI$154</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">給付資料!$A$1:$AE$30</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">理賠資料!$A$1:$AE$30</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -65,7 +65,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">檔整個拖進任一上傳格，工具會依工作表名稱自動分配到各檔案。</t>
+      <t xml:space="preserve">檔拖進上方的大框，工具會依工作表名稱自動分好。</t>
     </r>
   </si>
   <si>
@@ -75,7 +75,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">本檔為正確資料，工具檢核結果應為 </t>
+      <t xml:space="preserve">本檔是正確資料，檢查結果應該是 </t>
     </r>
     <r>
       <rPr>
@@ -92,7 +92,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">錯誤，可用來對照含錯誤版本。</t>
+      <t xml:space="preserve">個問題，可用來和含錯誤版本對照。</t>
     </r>
   </si>
   <si>
@@ -102,7 +102,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">欄位：承保／給付／上年度資料的欄位依《人壽保險業個人壽險填報手冊》</t>
+      <t xml:space="preserve">欄位：保單、理賠、去年保單資料的欄位依《人壽保險業個人壽險填報手冊》</t>
     </r>
     <r>
       <rPr>
@@ -136,7 +136,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">；數字欄位以文字儲存，保留前置 </t>
+      <t xml:space="preserve">；數字以文字儲存，保留開頭的 </t>
     </r>
     <r>
       <rPr>
@@ -166,7 +166,7 @@
     <t xml:space="preserve">內容</t>
   </si>
   <si>
-    <t xml:space="preserve">承保資料</t>
+    <t xml:space="preserve">保單資料</t>
   </si>
   <si>
     <r>
@@ -175,7 +175,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">保單資料（承保檔 </t>
+      <t xml:space="preserve">每張保單的申報資料（</t>
     </r>
     <r>
       <rPr>
@@ -184,7 +184,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">LFL</t>
+      <t xml:space="preserve">61 </t>
     </r>
     <r>
       <rPr>
@@ -192,7 +192,20 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">，</t>
+      <t xml:space="preserve">欄）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">理賠資料</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">每筆理賠給付的申報資料（</t>
     </r>
     <r>
       <rPr>
@@ -201,7 +214,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">61 </t>
+      <t xml:space="preserve">31 </t>
     </r>
     <r>
       <rPr>
@@ -213,7 +226,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">給付資料</t>
+    <t xml:space="preserve">客戶資料</t>
   </si>
   <si>
     <r>
@@ -222,7 +235,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">理賠資料（給付檔 </t>
+      <t xml:space="preserve">要保人（角色 </t>
     </r>
     <r>
       <rPr>
@@ -231,7 +244,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">LFD</t>
+      <t xml:space="preserve">1</t>
     </r>
     <r>
       <rPr>
@@ -239,7 +252,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">，</t>
+      <t xml:space="preserve">）與被保險人（角色 </t>
     </r>
     <r>
       <rPr>
@@ -248,7 +261,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">31 </t>
+      <t xml:space="preserve">2</t>
     </r>
     <r>
       <rPr>
@@ -256,53 +269,6 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">欄）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">客戶資料</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">要保人（角色 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）與被保險人（角色 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve">）</t>
     </r>
   </si>
@@ -313,22 +279,22 @@
     <t xml:space="preserve">商品代號、險種、繳費年期、起售日、停售日、替代代號</t>
   </si>
   <si>
-    <t xml:space="preserve">上年度承保資料</t>
-  </si>
-  <si>
-    <t xml:space="preserve">上年度申報檔，用於期初／期末結轉勾稽</t>
-  </si>
-  <si>
-    <t xml:space="preserve">控制總數</t>
-  </si>
-  <si>
-    <t xml:space="preserve">新契約、理賠、保單管理系統的控制總數，用於跨系統對帳</t>
+    <t xml:space="preserve">去年保單資料</t>
+  </si>
+  <si>
+    <t xml:space="preserve">去年申報的保單資料，用來確認去年底和今年初接得上</t>
+  </si>
+  <si>
+    <t xml:space="preserve">系統總數</t>
+  </si>
+  <si>
+    <t xml:space="preserve">新契約、理賠、保單系統各自的筆數與金額總數，用來核對申報資料</t>
   </si>
   <si>
     <t xml:space="preserve">資產負債表</t>
   </si>
   <si>
-    <t xml:space="preserve">科目餘額（含準備金），上層科目為公式加總</t>
+    <t xml:space="preserve">各科目餘額，上層科目用公式加總</t>
   </si>
   <si>
     <t xml:space="preserve">資產負債表平衡檢查</t>
@@ -14070,7 +14036,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="n">
-        <f aca="false">COUNTA(承保資料!A:A)-1</f>
+        <f aca="false">COUNTA(保單資料!A:A)-1</f>
         <v>153</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -14082,7 +14048,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="n">
-        <f aca="false">COUNTA(給付資料!A:A)-1</f>
+        <f aca="false">COUNTA(理賠資料!A:A)-1</f>
         <v>29</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -14118,7 +14084,7 @@
         <v>16</v>
       </c>
       <c r="B13" s="2" t="n">
-        <f aca="false">COUNTA(上年度承保資料!A:A)-1</f>
+        <f aca="false">COUNTA(去年保單資料!A:A)-1</f>
         <v>107</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -14130,7 +14096,7 @@
         <v>18</v>
       </c>
       <c r="B14" s="2" t="n">
-        <f aca="false">COUNTA(控制總數!A:A)-1</f>
+        <f aca="false">COUNTA(系統總數!A:A)-1</f>
         <v>25</v>
       </c>
       <c r="C14" s="2" t="s">
